--- a/clients/luxhomme/ozon-media/weekly-spend/Luxhomme_Ozon-media_2026-10-19_25.xlsx
+++ b/clients/luxhomme/ozon-media/weekly-spend/Luxhomme_Ozon-media_2026-10-19_25.xlsx
@@ -709,10 +709,10 @@
       <c r="B3" s="2" t="n">
         <v>46314</v>
       </c>
-      <c r="C3" t="n">
-        <v>1592</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="3" t="n">
+        <v>1592.4</v>
+      </c>
+      <c r="D3" s="3">
         <f>IF(F3= "директ", C3/1.22, C3)</f>
         <v/>
       </c>
@@ -744,10 +744,10 @@
       <c r="B4" s="2" t="n">
         <v>46315</v>
       </c>
-      <c r="C4" t="n">
-        <v>1624</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="3" t="n">
+        <v>1624.61</v>
+      </c>
+      <c r="D4" s="3">
         <f>IF(F4= "директ", C4/1.22, C4)</f>
         <v/>
       </c>
@@ -779,10 +779,10 @@
       <c r="B5" s="2" t="n">
         <v>46316</v>
       </c>
-      <c r="C5" t="n">
-        <v>1663</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="3" t="n">
+        <v>1663.38</v>
+      </c>
+      <c r="D5" s="3">
         <f>IF(F5= "директ", C5/1.22, C5)</f>
         <v/>
       </c>
@@ -814,10 +814,10 @@
       <c r="B6" s="2" t="n">
         <v>46317</v>
       </c>
-      <c r="C6" t="n">
-        <v>3133</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="3" t="n">
+        <v>3133.75</v>
+      </c>
+      <c r="D6" s="3">
         <f>IF(F6= "директ", C6/1.22, C6)</f>
         <v/>
       </c>
@@ -849,10 +849,10 @@
       <c r="B7" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="3" t="n">
+        <v>1312.06</v>
+      </c>
+      <c r="D7" s="3">
         <f>IF(F7= "директ", C7/1.22, C7)</f>
         <v/>
       </c>
@@ -884,10 +884,10 @@
       <c r="B8" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C8" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="3" t="n">
+        <v>1145.23</v>
+      </c>
+      <c r="D8" s="3">
         <f>IF(F8= "директ", C8/1.22, C8)</f>
         <v/>
       </c>
@@ -919,10 +919,10 @@
       <c r="B9" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C9" t="n">
-        <v>1323</v>
-      </c>
-      <c r="D9">
+      <c r="C9" s="3" t="n">
+        <v>1323.08</v>
+      </c>
+      <c r="D9" s="3">
         <f>IF(F9= "директ", C9/1.22, C9)</f>
         <v/>
       </c>
@@ -954,10 +954,10 @@
       <c r="B10" s="2" t="n">
         <v>46314</v>
       </c>
-      <c r="C10" t="n">
-        <v>1592</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="3" t="n">
+        <v>1592.4</v>
+      </c>
+      <c r="D10" s="3">
         <f>IF(F10= "директ", C10/1.22, C10)</f>
         <v/>
       </c>
@@ -989,10 +989,10 @@
       <c r="B11" s="2" t="n">
         <v>46315</v>
       </c>
-      <c r="C11" t="n">
-        <v>1624</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="3" t="n">
+        <v>1624.61</v>
+      </c>
+      <c r="D11" s="3">
         <f>IF(F11= "директ", C11/1.22, C11)</f>
         <v/>
       </c>
@@ -1024,10 +1024,10 @@
       <c r="B12" s="2" t="n">
         <v>46316</v>
       </c>
-      <c r="C12" t="n">
-        <v>1663</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="3" t="n">
+        <v>1663.38</v>
+      </c>
+      <c r="D12" s="3">
         <f>IF(F12= "директ", C12/1.22, C12)</f>
         <v/>
       </c>
@@ -1059,10 +1059,10 @@
       <c r="B13" s="2" t="n">
         <v>46317</v>
       </c>
-      <c r="C13" t="n">
-        <v>3133</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="3" t="n">
+        <v>3133.75</v>
+      </c>
+      <c r="D13" s="3">
         <f>IF(F13= "директ", C13/1.22, C13)</f>
         <v/>
       </c>
@@ -1094,10 +1094,10 @@
       <c r="B14" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C14" t="n">
-        <v>1312</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="3" t="n">
+        <v>1312.06</v>
+      </c>
+      <c r="D14" s="3">
         <f>IF(F14= "директ", C14/1.22, C14)</f>
         <v/>
       </c>
@@ -1129,10 +1129,10 @@
       <c r="B15" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C15" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="3" t="n">
+        <v>1145.23</v>
+      </c>
+      <c r="D15" s="3">
         <f>IF(F15= "директ", C15/1.22, C15)</f>
         <v/>
       </c>
@@ -1164,10 +1164,10 @@
       <c r="B16" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C16" t="n">
-        <v>1323</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="3" t="n">
+        <v>1323.08</v>
+      </c>
+      <c r="D16" s="3">
         <f>IF(F16= "директ", C16/1.22, C16)</f>
         <v/>
       </c>
@@ -1199,10 +1199,10 @@
       <c r="B17" s="2" t="n">
         <v>46314</v>
       </c>
-      <c r="C17" t="n">
-        <v>1592</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="3" t="n">
+        <v>1592.4</v>
+      </c>
+      <c r="D17" s="3">
         <f>IF(F17= "директ", C17/1.22, C17)</f>
         <v/>
       </c>
@@ -1234,10 +1234,10 @@
       <c r="B18" s="2" t="n">
         <v>46315</v>
       </c>
-      <c r="C18" t="n">
-        <v>1624</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="3" t="n">
+        <v>1624.61</v>
+      </c>
+      <c r="D18" s="3">
         <f>IF(F18= "директ", C18/1.22, C18)</f>
         <v/>
       </c>
@@ -1269,10 +1269,10 @@
       <c r="B19" s="2" t="n">
         <v>46316</v>
       </c>
-      <c r="C19" t="n">
-        <v>1663</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="3" t="n">
+        <v>1663.38</v>
+      </c>
+      <c r="D19" s="3">
         <f>IF(F19= "директ", C19/1.22, C19)</f>
         <v/>
       </c>
@@ -1304,10 +1304,10 @@
       <c r="B20" s="2" t="n">
         <v>46317</v>
       </c>
-      <c r="C20" t="n">
-        <v>3133</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="3" t="n">
+        <v>3133.75</v>
+      </c>
+      <c r="D20" s="3">
         <f>IF(F20= "директ", C20/1.22, C20)</f>
         <v/>
       </c>
@@ -1339,10 +1339,10 @@
       <c r="B21" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C21" t="n">
-        <v>1312</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="3" t="n">
+        <v>1312.06</v>
+      </c>
+      <c r="D21" s="3">
         <f>IF(F21= "директ", C21/1.22, C21)</f>
         <v/>
       </c>
@@ -1374,10 +1374,10 @@
       <c r="B22" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C22" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="3" t="n">
+        <v>1145.23</v>
+      </c>
+      <c r="D22" s="3">
         <f>IF(F22= "директ", C22/1.22, C22)</f>
         <v/>
       </c>
@@ -1409,10 +1409,10 @@
       <c r="B23" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C23" t="n">
-        <v>1323</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="3" t="n">
+        <v>1323.08</v>
+      </c>
+      <c r="D23" s="3">
         <f>IF(F23= "директ", C23/1.22, C23)</f>
         <v/>
       </c>
@@ -1444,10 +1444,10 @@
       <c r="B24" s="2" t="n">
         <v>46314</v>
       </c>
-      <c r="C24" t="n">
-        <v>1592</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="3" t="n">
+        <v>1592.4</v>
+      </c>
+      <c r="D24" s="3">
         <f>IF(F24= "директ", C24/1.22, C24)</f>
         <v/>
       </c>
@@ -1479,10 +1479,10 @@
       <c r="B25" s="2" t="n">
         <v>46315</v>
       </c>
-      <c r="C25" t="n">
-        <v>1624</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="3" t="n">
+        <v>1624.61</v>
+      </c>
+      <c r="D25" s="3">
         <f>IF(F25= "директ", C25/1.22, C25)</f>
         <v/>
       </c>
@@ -1514,10 +1514,10 @@
       <c r="B26" s="2" t="n">
         <v>46316</v>
       </c>
-      <c r="C26" t="n">
-        <v>1663</v>
-      </c>
-      <c r="D26">
+      <c r="C26" s="3" t="n">
+        <v>1663.38</v>
+      </c>
+      <c r="D26" s="3">
         <f>IF(F26= "директ", C26/1.22, C26)</f>
         <v/>
       </c>
@@ -1549,10 +1549,10 @@
       <c r="B27" s="2" t="n">
         <v>46317</v>
       </c>
-      <c r="C27" t="n">
-        <v>3133</v>
-      </c>
-      <c r="D27">
+      <c r="C27" s="3" t="n">
+        <v>3133.75</v>
+      </c>
+      <c r="D27" s="3">
         <f>IF(F27= "директ", C27/1.22, C27)</f>
         <v/>
       </c>
@@ -1584,10 +1584,10 @@
       <c r="B28" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C28" t="n">
-        <v>1312</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="3" t="n">
+        <v>1312.06</v>
+      </c>
+      <c r="D28" s="3">
         <f>IF(F28= "директ", C28/1.22, C28)</f>
         <v/>
       </c>
@@ -1619,10 +1619,10 @@
       <c r="B29" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C29" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D29">
+      <c r="C29" s="3" t="n">
+        <v>1145.23</v>
+      </c>
+      <c r="D29" s="3">
         <f>IF(F29= "директ", C29/1.22, C29)</f>
         <v/>
       </c>
@@ -1654,10 +1654,10 @@
       <c r="B30" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C30" t="n">
-        <v>1323</v>
-      </c>
-      <c r="D30">
+      <c r="C30" s="3" t="n">
+        <v>1323.08</v>
+      </c>
+      <c r="D30" s="3">
         <f>IF(F30= "директ", C30/1.22, C30)</f>
         <v/>
       </c>
@@ -1689,10 +1689,10 @@
       <c r="B31" s="2" t="n">
         <v>46314</v>
       </c>
-      <c r="C31" t="n">
-        <v>1592</v>
-      </c>
-      <c r="D31">
+      <c r="C31" s="3" t="n">
+        <v>1592.4</v>
+      </c>
+      <c r="D31" s="3">
         <f>IF(F31= "директ", C31/1.22, C31)</f>
         <v/>
       </c>
@@ -1724,10 +1724,10 @@
       <c r="B32" s="2" t="n">
         <v>46315</v>
       </c>
-      <c r="C32" t="n">
-        <v>1624</v>
-      </c>
-      <c r="D32">
+      <c r="C32" s="3" t="n">
+        <v>1624.61</v>
+      </c>
+      <c r="D32" s="3">
         <f>IF(F32= "директ", C32/1.22, C32)</f>
         <v/>
       </c>
@@ -1759,10 +1759,10 @@
       <c r="B33" s="2" t="n">
         <v>46316</v>
       </c>
-      <c r="C33" t="n">
-        <v>1663</v>
-      </c>
-      <c r="D33">
+      <c r="C33" s="3" t="n">
+        <v>1663.38</v>
+      </c>
+      <c r="D33" s="3">
         <f>IF(F33= "директ", C33/1.22, C33)</f>
         <v/>
       </c>
@@ -1794,10 +1794,10 @@
       <c r="B34" s="2" t="n">
         <v>46317</v>
       </c>
-      <c r="C34" t="n">
-        <v>3133</v>
-      </c>
-      <c r="D34">
+      <c r="C34" s="3" t="n">
+        <v>3133.75</v>
+      </c>
+      <c r="D34" s="3">
         <f>IF(F34= "директ", C34/1.22, C34)</f>
         <v/>
       </c>
@@ -1829,10 +1829,10 @@
       <c r="B35" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C35" t="n">
-        <v>1312</v>
-      </c>
-      <c r="D35">
+      <c r="C35" s="3" t="n">
+        <v>1312.06</v>
+      </c>
+      <c r="D35" s="3">
         <f>IF(F35= "директ", C35/1.22, C35)</f>
         <v/>
       </c>
@@ -1864,10 +1864,10 @@
       <c r="B36" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C36" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D36">
+      <c r="C36" s="3" t="n">
+        <v>1145.23</v>
+      </c>
+      <c r="D36" s="3">
         <f>IF(F36= "директ", C36/1.22, C36)</f>
         <v/>
       </c>
@@ -1899,10 +1899,10 @@
       <c r="B37" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C37" t="n">
-        <v>1323</v>
-      </c>
-      <c r="D37">
+      <c r="C37" s="3" t="n">
+        <v>1323.08</v>
+      </c>
+      <c r="D37" s="3">
         <f>IF(F37= "директ", C37/1.22, C37)</f>
         <v/>
       </c>
